--- a/tests/ExcelLoadData/TieredLoads_Testing2.xlsx
+++ b/tests/ExcelLoadData/TieredLoads_Testing2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dlvilla\TEMP\TEB\tests\ExcelLoadData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09F9D48-0A4C-47EC-82D0-EFA02CD65425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7C7081-4F6B-4D6C-A23B-D0C8941ED9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" xr2:uid="{1F2B6D78-A821-4296-99B9-3A0B6B938907}"/>
+    <workbookView xWindow="4620" yWindow="3420" windowWidth="21600" windowHeight="11385" firstSheet="11" activeTab="14" xr2:uid="{1F2B6D78-A821-4296-99B9-3A0B6B938907}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticElectricLoads" sheetId="1" r:id="rId1"/>
@@ -3827,31 +3827,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{B6E24FE8-171F-4DD9-85AE-EFE65DD5B312}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Villa, Daniel L:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-This comes from 00_ANEJO D.2-Plano-2053-calleCorta-LaPolilla-1un.pdf</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{503197ED-A21E-4811-8261-3F9E58AEA05B}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{503197ED-A21E-4811-8261-3F9E58AEA05B}">
       <text>
         <r>
           <rPr>
@@ -3875,31 +3851,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{77CCC27B-5F09-40D8-8D27-B1C1C568B3F5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Villa, Daniel L:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-This comes from 00_ANEJO D.2-Plano-2053-calleCorta-LaPolilla-1un.pdf</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{DB2A58B4-501A-4078-8B7B-6A2B3EC9A3CD}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{DB2A58B4-501A-4078-8B7B-6A2B3EC9A3CD}">
       <text>
         <r>
           <rPr>
@@ -3923,36 +3875,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{AEEC4A21-16AE-4A3D-A191-83F1114AAC35}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Villa, Daniel L:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-This comes from 00_ANEJO D.2-Plano-2053-calleCorta-LaPolilla-1un.pdf</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="159">
   <si>
     <t>Tier 1</t>
   </si>
@@ -60635,7 +60563,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9025A5CD-2B5D-4B93-BC08-61D2C05FA2C5}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.85546875" bestFit="1" customWidth="1"/>
@@ -60675,73 +60603,49 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" t="s">
         <v>105</v>
       </c>
     </row>
@@ -62613,6 +62517,7 @@
     <col min="10" max="11" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="30" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>

--- a/tests/ExcelLoadData/TieredLoads_Testing2.xlsx
+++ b/tests/ExcelLoadData/TieredLoads_Testing2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dlvilla\TEMP\TEB\tests\ExcelLoadData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7C7081-4F6B-4D6C-A23B-D0C8941ED9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133C5C0B-426B-4543-B8A9-246B52ECF464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="3420" windowWidth="21600" windowHeight="11385" firstSheet="11" activeTab="14" xr2:uid="{1F2B6D78-A821-4296-99B9-3A0B6B938907}"/>
+    <workbookView xWindow="7545" yWindow="4095" windowWidth="21600" windowHeight="11385" xr2:uid="{1F2B6D78-A821-4296-99B9-3A0B6B938907}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticElectricLoads" sheetId="1" r:id="rId1"/>
@@ -4217,9 +4217,6 @@
     <t>TypicalRange</t>
   </si>
   <si>
-    <t>Per Area (W = False or W/m2 = True?)</t>
-  </si>
-  <si>
     <t>Townhome2B_Elev_Home_Medical</t>
   </si>
   <si>
@@ -4368,6 +4365,9 @@
   </si>
   <si>
     <t>Energy (kWh/day or kWh/day/m2)</t>
+  </si>
+  <si>
+    <t>Per Area (kWh = False or kWh/m2 = True?)</t>
   </si>
 </sst>
 </file>
@@ -4857,10 +4857,10 @@
         <v>65</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>88</v>
@@ -4869,10 +4869,10 @@
         <v>61</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4889,10 +4889,10 @@
         <v>2000</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" t="s">
-        <v>109</v>
+        <v>139</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="G2">
         <v>0.8</v>
@@ -4915,10 +4915,10 @@
         <v>2000</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3">
         <v>0.8</v>
@@ -4941,10 +4941,10 @@
         <v>2000</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G4">
         <v>0.8</v>
@@ -4967,10 +4967,10 @@
         <v>2000</v>
       </c>
       <c r="E5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G5">
         <v>0.8</v>
@@ -4995,8 +4995,8 @@
       <c r="E6" t="s">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>109</v>
+      <c r="F6" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="G6">
         <v>0.8</v>
@@ -5022,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7">
         <v>0.8</v>
@@ -5048,7 +5048,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G8">
         <v>0.8</v>
@@ -5074,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G9">
         <v>0.8</v>
@@ -5099,7 +5099,7 @@
       <c r="E10" t="s">
         <v>0</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G10">
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G13">
         <v>0.8</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G14">
         <v>0.8</v>
@@ -5230,7 +5230,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G15">
         <v>0.8</v>
@@ -5255,7 +5255,7 @@
       <c r="E16" t="s">
         <v>1</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G16">
@@ -5334,7 +5334,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G19">
         <v>0.8</v>
@@ -5360,7 +5360,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G20">
         <v>0.8</v>
@@ -5386,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G21">
         <v>0.8</v>
@@ -5411,7 +5411,7 @@
       <c r="E22" t="s">
         <v>2</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G22">
@@ -5490,7 +5490,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G25">
         <v>0.8</v>
@@ -5516,7 +5516,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G26">
         <v>0.8</v>
@@ -5542,7 +5542,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G27">
         <v>0.8</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" t="s">
         <v>143</v>
-      </c>
-      <c r="B28" t="s">
-        <v>144</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
@@ -5567,7 +5567,7 @@
       <c r="E28" t="s">
         <v>1</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G28">
@@ -5579,10 +5579,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" t="s">
         <v>143</v>
-      </c>
-      <c r="B29" t="s">
-        <v>144</v>
       </c>
       <c r="C29" t="b">
         <v>0</v>
@@ -5605,10 +5605,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" t="s">
         <v>143</v>
-      </c>
-      <c r="B30" t="s">
-        <v>144</v>
       </c>
       <c r="C30" t="b">
         <v>0</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" t="s">
         <v>143</v>
-      </c>
-      <c r="B31" t="s">
-        <v>144</v>
       </c>
       <c r="C31" t="b">
         <v>0</v>
@@ -5646,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G31">
         <v>0.8</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" t="s">
         <v>143</v>
-      </c>
-      <c r="B32" t="s">
-        <v>144</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
@@ -5672,7 +5672,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G32">
         <v>0.8</v>
@@ -5683,10 +5683,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" t="s">
         <v>143</v>
-      </c>
-      <c r="B33" t="s">
-        <v>144</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
@@ -5698,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G33">
         <v>0.8</v>
@@ -5709,10 +5709,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" t="s">
         <v>128</v>
-      </c>
-      <c r="B34" t="s">
-        <v>129</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
@@ -5724,7 +5724,7 @@
       <c r="E34" t="s">
         <v>0</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G34">
@@ -5736,10 +5736,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" t="s">
         <v>128</v>
-      </c>
-      <c r="B35" t="s">
-        <v>129</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" t="s">
         <v>128</v>
-      </c>
-      <c r="B36" t="s">
-        <v>129</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" t="s">
         <v>128</v>
-      </c>
-      <c r="B37" t="s">
-        <v>129</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G37">
         <v>0.8</v>
@@ -5817,10 +5817,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" t="s">
         <v>128</v>
-      </c>
-      <c r="B38" t="s">
-        <v>129</v>
       </c>
       <c r="C38" t="b">
         <v>0</v>
@@ -5832,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G38">
         <v>0.8</v>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" t="s">
         <v>128</v>
-      </c>
-      <c r="B39" t="s">
-        <v>129</v>
       </c>
       <c r="C39" t="b">
         <v>0</v>
@@ -5858,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G39">
         <v>0.8</v>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
         <v>130</v>
-      </c>
-      <c r="B40" t="s">
-        <v>131</v>
       </c>
       <c r="C40" t="b">
         <v>0</v>
@@ -5881,9 +5881,9 @@
         <v>500</v>
       </c>
       <c r="E40" t="s">
-        <v>140</v>
-      </c>
-      <c r="F40" t="s">
+        <v>139</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G40">
@@ -5895,10 +5895,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" t="s">
         <v>130</v>
-      </c>
-      <c r="B41" t="s">
-        <v>131</v>
       </c>
       <c r="C41" t="b">
         <v>0</v>
@@ -5907,7 +5907,7 @@
         <v>500</v>
       </c>
       <c r="E41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F41" t="s">
         <v>101</v>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" t="s">
         <v>130</v>
-      </c>
-      <c r="B42" t="s">
-        <v>131</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
@@ -5933,7 +5933,7 @@
         <v>500</v>
       </c>
       <c r="E42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F42" t="s">
         <v>105</v>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" t="s">
         <v>130</v>
-      </c>
-      <c r="B43" t="s">
-        <v>131</v>
       </c>
       <c r="C43" t="b">
         <v>0</v>
@@ -5959,10 +5959,10 @@
         <v>500</v>
       </c>
       <c r="E43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G43">
         <v>0.8</v>
@@ -5985,9 +5985,9 @@
         <v>3000</v>
       </c>
       <c r="E44" t="s">
-        <v>140</v>
-      </c>
-      <c r="F44" t="s">
+        <v>139</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G44">
@@ -6011,7 +6011,7 @@
         <v>3000</v>
       </c>
       <c r="E45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F45" t="s">
         <v>101</v>
@@ -6037,7 +6037,7 @@
         <v>3000</v>
       </c>
       <c r="E46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F46" t="s">
         <v>105</v>
@@ -6063,10 +6063,10 @@
         <v>3000</v>
       </c>
       <c r="E47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G47">
         <v>0.8</v>
@@ -6077,10 +6077,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" t="s">
         <v>132</v>
-      </c>
-      <c r="B48" t="s">
-        <v>133</v>
       </c>
       <c r="C48" t="b">
         <v>0</v>
@@ -6091,7 +6091,7 @@
       <c r="E48" t="s">
         <v>0</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G48">
@@ -6103,10 +6103,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" t="s">
         <v>132</v>
-      </c>
-      <c r="B49" t="s">
-        <v>133</v>
       </c>
       <c r="C49" t="b">
         <v>0</v>
@@ -6129,10 +6129,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
         <v>132</v>
-      </c>
-      <c r="B50" t="s">
-        <v>133</v>
       </c>
       <c r="C50" t="b">
         <v>0</v>
@@ -6155,10 +6155,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" t="s">
         <v>132</v>
-      </c>
-      <c r="B51" t="s">
-        <v>133</v>
       </c>
       <c r="C51" t="b">
         <v>0</v>
@@ -6170,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G51">
         <v>0.8</v>
@@ -6181,10 +6181,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C52" t="b">
         <v>0</v>
@@ -6195,7 +6195,7 @@
       <c r="E52" t="s">
         <v>2</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="7" t="s">
         <v>100</v>
       </c>
       <c r="G52">
@@ -6207,10 +6207,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C53" t="b">
         <v>0</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C54" t="b">
         <v>0</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B55" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C55" t="b">
         <v>0</v>
@@ -6274,7 +6274,7 @@
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G55">
         <v>0.8</v>
@@ -6309,7 +6309,7 @@
         <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -6429,7 +6429,7 @@
         <v>68</v>
       </c>
       <c r="K1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -59530,13 +59530,13 @@
         <v>105</v>
       </c>
       <c r="E1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1" t="s">
         <v>136</v>
-      </c>
-      <c r="G1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -59553,13 +59553,13 @@
         <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" t="s">
         <v>136</v>
-      </c>
-      <c r="G2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -59794,7 +59794,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13">
         <v>0.11</v>
@@ -59817,7 +59817,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" s="7">
         <v>1280</v>
@@ -59840,7 +59840,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -59857,7 +59857,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -59874,7 +59874,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -59998,10 +59998,10 @@
         <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -60098,7 +60098,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B27" s="7">
         <v>1.4530000000000001</v>
@@ -60282,7 +60282,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B35" t="b">
         <v>1</v>
@@ -60305,7 +60305,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" t="b">
         <v>0</v>
@@ -60328,7 +60328,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F37">
         <v>2.5</v>
@@ -60363,7 +60363,7 @@
         <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -60386,13 +60386,13 @@
         <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -60406,13 +60406,13 @@
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -60426,13 +60426,13 @@
         <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -60446,61 +60446,61 @@
         <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
         <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -60517,10 +60517,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -60537,22 +60537,22 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
         <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -60571,7 +60571,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
         <v>61</v>
@@ -60579,7 +60579,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
         <v>100</v>
@@ -60587,7 +60587,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
         <v>101</v>
@@ -60595,7 +60595,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
         <v>105</v>
@@ -60603,7 +60603,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
         <v>100</v>
@@ -60611,23 +60611,23 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
         <v>100</v>
@@ -60635,7 +60635,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
         <v>101</v>
@@ -60643,7 +60643,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
         <v>105</v>
@@ -60690,7 +60690,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -60704,7 +60704,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -60718,12 +60718,12 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -60732,12 +60732,12 @@
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -60746,12 +60746,12 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -60760,7 +60760,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -60807,7 +60807,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -60821,7 +60821,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -60835,7 +60835,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -60891,7 +60891,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -60905,7 +60905,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -60919,7 +60919,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -60975,7 +60975,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -60989,7 +60989,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -61003,7 +61003,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -61043,16 +61043,16 @@
         <v>30</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>88</v>
@@ -61081,7 +61081,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -61107,7 +61107,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -61133,12 +61133,12 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -61159,12 +61159,12 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -61185,12 +61185,12 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -61211,7 +61211,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -61294,7 +61294,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -61320,7 +61320,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -61346,7 +61346,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -61450,7 +61450,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -61476,7 +61476,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -61502,7 +61502,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -61606,7 +61606,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -61632,7 +61632,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -61658,7 +61658,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -61684,7 +61684,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="7">
         <v>1</v>
@@ -61749,7 +61749,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -61763,7 +61763,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -61777,12 +61777,12 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -61791,12 +61791,12 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -61805,12 +61805,12 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -61819,7 +61819,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -61866,7 +61866,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -61880,7 +61880,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -61894,7 +61894,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -61950,7 +61950,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -61964,7 +61964,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -61978,7 +61978,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -62034,7 +62034,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -62048,7 +62048,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -62062,7 +62062,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -62076,7 +62076,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -62085,12 +62085,12 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -62099,12 +62099,12 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -62113,12 +62113,12 @@
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -62127,7 +62127,7 @@
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -62172,7 +62172,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -62186,7 +62186,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -62200,12 +62200,12 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -62214,12 +62214,12 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6">
         <v>125</v>
@@ -62228,12 +62228,12 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7">
         <v>125</v>
@@ -62242,7 +62242,7 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -62289,7 +62289,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -62303,7 +62303,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -62317,7 +62317,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -62373,7 +62373,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B17">
         <v>8</v>
@@ -62387,7 +62387,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B18">
         <v>300</v>
@@ -62401,7 +62401,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19">
         <v>300</v>
@@ -62457,7 +62457,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -62471,7 +62471,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -62485,7 +62485,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -62531,7 +62531,7 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
         <v>22</v>
@@ -62546,7 +62546,7 @@
         <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H1" t="s">
         <v>34</v>
@@ -62561,37 +62561,37 @@
         <v>87</v>
       </c>
       <c r="L1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N1" t="s">
         <v>107</v>
       </c>
       <c r="O1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P1" t="s">
         <v>133</v>
       </c>
-      <c r="P1" t="s">
-        <v>134</v>
-      </c>
       <c r="Q1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="V1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -64536,16 +64536,16 @@
         <v>30</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -64697,16 +64697,16 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F8" t="s">
         <v>148</v>
       </c>
-      <c r="F8" t="s">
-        <v>149</v>
-      </c>
       <c r="G8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
